--- a/po_template.xlsx
+++ b/po_template.xlsx
@@ -1,252 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC4F59B-53E4-2D4F-80F2-3BED3D6EB3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="نموذج طلب شراء" sheetId="1" r:id="rId1"/>
+    <sheet name="نموذج طلب شراء" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>NO. 0144</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
-  </si>
-  <si>
-    <t>بيانات السيارة والسائق</t>
-  </si>
-  <si>
-    <t>اسم السائق:</t>
-  </si>
-  <si>
-    <t>الفرع:</t>
-  </si>
-  <si>
-    <t>الدمام</t>
-  </si>
-  <si>
-    <t>الوظيفة:</t>
-  </si>
-  <si>
-    <t>نوع السيارة:</t>
-  </si>
-  <si>
-    <t>رقم اللوحة:</t>
-  </si>
-  <si>
-    <t>الموديل:</t>
-  </si>
-  <si>
-    <t>قطع الغيار</t>
-  </si>
-  <si>
-    <t>م</t>
-  </si>
-  <si>
-    <t>البيان</t>
-  </si>
-  <si>
-    <t>الكمية</t>
-  </si>
-  <si>
-    <t>السعر</t>
-  </si>
-  <si>
-    <t>القيمة</t>
-  </si>
-  <si>
-    <t>ملاحظات</t>
-  </si>
-  <si>
-    <t>الإصلاح</t>
-  </si>
-  <si>
-    <t>الوصف</t>
-  </si>
-  <si>
-    <t>الكفرات</t>
-  </si>
-  <si>
-    <t>تاريخ التغيير</t>
-  </si>
-  <si>
-    <t>العدد</t>
-  </si>
-  <si>
-    <t>أمامية</t>
-  </si>
-  <si>
-    <t>خلفية</t>
-  </si>
-  <si>
-    <t>قراءة سابقة</t>
-  </si>
-  <si>
-    <t>قراءة حالية</t>
-  </si>
-  <si>
-    <t>المسافة</t>
-  </si>
-  <si>
-    <t>البطاريات</t>
-  </si>
-  <si>
-    <t>المقاس</t>
-  </si>
-  <si>
-    <t>أمبير</t>
-  </si>
-  <si>
-    <t>السعر للوحدة</t>
-  </si>
-  <si>
-    <t>التاريخ</t>
-  </si>
-  <si>
-    <t>الإجمالي شامل الضريبة</t>
-  </si>
-  <si>
-    <t>السائق</t>
-  </si>
-  <si>
-    <t>الميكانيكي</t>
-  </si>
-  <si>
-    <t>قسم الحركة</t>
-  </si>
-  <si>
-    <t>مسئول الشراء</t>
-  </si>
-  <si>
-    <t>الحسابات</t>
-  </si>
-  <si>
-    <t>مدير الفرع</t>
-  </si>
-  <si>
-    <t>اعتماد الإدارة</t>
-  </si>
-  <si>
-    <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
-  </si>
-  <si>
-    <t>ملاحظات هامة</t>
-  </si>
-  <si>
-    <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
-2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
-3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
-4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_ * #,##0.00_)&quot;ر.س.&quot;_ ;_ * \(#,##0.00\)&quot;ر.س.&quot;_ ;_ * &quot;-&quot;??_)&quot;ر.س.&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;ر.س.&quot;_-;\-* #,##0\ &quot;ر.س.&quot;_-;_-* &quot;-&quot;\ &quot;ر.س.&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
+      <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Helvetica"/>
+      <color indexed="11"/>
       <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Helvetica"/>
     </font>
     <font>
-      <b/>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color indexed="11"/>
       <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Helvetica"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="178"/>
+      <family val="2"/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="178"/>
     </font>
     <font>
-      <b/>
+      <name val="Sakkal Majalla"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Sakkal Majalla"/>
     </font>
     <font>
+      <name val="Sakkal Majalla"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Sakkal Majalla"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -265,24 +107,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -468,174 +310,210 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="62">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="64">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
-    <cellStyle name="عادي 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="عادي 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -705,14 +583,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1790,846 +1660,995 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
-  <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A2:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="8.94921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.01171875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.97265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.01171875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.97265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.55859375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.859375" style="1" customWidth="1"/>
-    <col min="11" max="15" width="8.94921875" style="1" customWidth="1"/>
-    <col min="16" max="17" width="8.82421875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.82421875" style="1"/>
+    <col width="8.94921875" customWidth="1" style="46" min="1" max="2"/>
+    <col width="12.01171875" customWidth="1" style="46" min="3" max="3"/>
+    <col width="13.97265625" customWidth="1" style="46" min="4" max="4"/>
+    <col width="12.01171875" customWidth="1" style="46" min="5" max="5"/>
+    <col width="13.97265625" customWidth="1" style="46" min="6" max="7"/>
+    <col width="14.953125" customWidth="1" style="46" min="8" max="8"/>
+    <col width="9.55859375" customWidth="1" style="46" min="9" max="9"/>
+    <col width="19.859375" customWidth="1" style="46" min="10" max="10"/>
+    <col width="8.94921875" customWidth="1" style="46" min="11" max="15"/>
+    <col width="8.82421875" customWidth="1" style="46" min="16" max="17"/>
+    <col width="8.82421875" customWidth="1" style="46" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="27" t="s">
+    <row r="1" ht="35.25" customHeight="1" s="46"/>
+    <row r="2" ht="56.25" customHeight="1" s="46">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" s="46">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="27" t="inlineStr">
+        <is>
+          <t>NO. 000001</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="27" customHeight="1" s="46" thickBot="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="n"/>
+      <c r="G4" s="52" t="n"/>
+      <c r="H4" s="52" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="9.75" customHeight="1" s="46">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="46">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>بيانات السيارة والسائق</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" s="46">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>اسم السائق:</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>الفرع:</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>الدمام</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>الوظيفة:</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>سائق</t>
+        </is>
+      </c>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="18.4" customHeight="1" s="46">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>نوع السيارة:</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="inlineStr"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>رقم اللوحة:</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>الموديل:</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="inlineStr"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18.4" customHeight="1" s="46">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="62" t="inlineStr">
+        <is>
+          <t>عداد السيارة:</t>
+        </is>
+      </c>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="37" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="17.45" customHeight="1" s="46">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>قطع الغيار</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="22.35" customHeight="1" s="46">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>البيان</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>السعر</t>
+        </is>
+      </c>
+      <c r="I11" s="41" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="J11" s="41" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="18.95" customHeight="1" s="46">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
+      <c r="D12" s="36" t="inlineStr"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="36" t="inlineStr"/>
+      <c r="K12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="17.1" customHeight="1" s="46">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="51" t="s">
+      <c r="D13" s="40" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="33" t="n"/>
+      <c r="I13" s="33" t="n"/>
+      <c r="J13" s="40" t="n"/>
+      <c r="K13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="17.1" customHeight="1" s="46">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="24">
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="17.1" customHeight="1" s="46">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="17.45" customHeight="1" s="46">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>الإصلاح</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="22.15" customHeight="1" s="46">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="56" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="I17" s="56" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="J17" s="57" t="n"/>
+      <c r="K17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="18.95" customHeight="1" s="46">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="24">
+      <c r="D18" s="36" t="inlineStr"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="inlineStr"/>
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="17.1" customHeight="1" s="46">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="24">
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="40" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="17.1" customHeight="1" s="46">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="57"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="24">
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="38" t="n"/>
+      <c r="K20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="17.1" customHeight="1" s="46">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="17.45" customHeight="1" s="46">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>الكفرات</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="38" t="n"/>
+      <c r="K22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="22.15" customHeight="1" s="46">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>تاريخ التغيير</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>العدد</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>أمامية</t>
+        </is>
+      </c>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>خلفية</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="inlineStr">
+        <is>
+          <t>قراءة سابقة</t>
+        </is>
+      </c>
+      <c r="I23" s="41" t="inlineStr">
+        <is>
+          <t>قراءة حالية</t>
+        </is>
+      </c>
+      <c r="J23" s="41" t="inlineStr">
+        <is>
+          <t>المسافة</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="18.95" customHeight="1" s="46">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="24">
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="17.1" customHeight="1" s="46">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="24">
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="17.1" customHeight="1" s="46">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="24">
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="17.1" customHeight="1" s="46">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="17.45" customHeight="1" s="46">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>البطاريات</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="37" t="n"/>
+      <c r="H28" s="37" t="n"/>
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="38" t="n"/>
+      <c r="K28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="22.15" customHeight="1" s="46">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>العدد</t>
+        </is>
+      </c>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="H29" s="41" t="inlineStr">
+        <is>
+          <t>أمبير</t>
+        </is>
+      </c>
+      <c r="I29" s="41" t="inlineStr">
+        <is>
+          <t>السعر للوحدة</t>
+        </is>
+      </c>
+      <c r="J29" s="41" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="18.95" customHeight="1" s="46">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D30" s="36" t="inlineStr"/>
+      <c r="E30" s="38" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="inlineStr"/>
+      <c r="H30" s="36" t="inlineStr"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="17.1" customHeight="1" s="46">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="24">
-        <v>2</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="24">
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="40" t="n"/>
+      <c r="I31" s="40" t="n"/>
+      <c r="J31" s="40" t="n"/>
+      <c r="K31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="17.1" customHeight="1" s="46">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="24">
-        <v>1</v>
-      </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="24">
-        <v>2</v>
-      </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="24">
-        <v>3</v>
-      </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="3"/>
-    </row>
-    <row r="37" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="38" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="3"/>
-    </row>
-    <row r="39" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="8"/>
-    </row>
-    <row r="40" spans="1:11" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F40" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I40" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="30"/>
-    </row>
-    <row r="41" spans="1:11" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="2"/>
-      <c r="C42" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="17.1" customHeight="1" s="46">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="45" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="45" t="n"/>
+      <c r="H33" s="45" t="n"/>
+      <c r="I33" s="45" t="n"/>
+      <c r="J33" s="45" t="n"/>
+      <c r="K33" s="3" t="n"/>
+    </row>
+    <row r="34" ht="18.95" customHeight="1" s="46">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>قطع الغيار</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>الإصلاح</t>
+        </is>
+      </c>
+      <c r="E34" s="39" t="inlineStr">
+        <is>
+          <t>الكفرات</t>
+        </is>
+      </c>
+      <c r="F34" s="39" t="inlineStr">
+        <is>
+          <t>البطاريات</t>
+        </is>
+      </c>
+      <c r="G34" s="39" t="inlineStr">
+        <is>
+          <t>الإجمالي شامل الضريبة</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="39" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="n"/>
+      <c r="K34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="17.65" customHeight="1" s="46">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="35" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="38" t="n"/>
+      <c r="K35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="17.1" customHeight="1" s="46">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="I36" s="45" t="n"/>
+      <c r="K36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="18.6" customHeight="1" s="46">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>الإجمالي شامل الضريبة</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="37" t="n"/>
+      <c r="G37" s="37" t="n"/>
+      <c r="H37" s="37" t="n"/>
+      <c r="I37" s="37" t="n"/>
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="46" thickBot="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="55" t="n"/>
+      <c r="H38" s="55" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="5.25" customHeight="1" s="46">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="21" customFormat="1" customHeight="1" s="31">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>السائق</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>الميكانيكي</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>قسم الحركة</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
+          <t>مسئول الشراء</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>الحسابات</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>مدير الفرع</t>
+        </is>
+      </c>
+      <c r="I40" s="60" t="inlineStr">
+        <is>
+          <t>اعتماد الإدارة</t>
+        </is>
+      </c>
+      <c r="J40" s="61" t="n"/>
+      <c r="K40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="63" customHeight="1" s="46" thickBot="1">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="17.25" customHeight="1" s="46">
+      <c r="A42" s="2" t="n"/>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="44" t="n"/>
+      <c r="H42" s="44" t="n"/>
+      <c r="I42" s="44" t="n"/>
+      <c r="J42" s="44" t="n"/>
+      <c r="K42" s="3" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="46">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="47" t="inlineStr">
+        <is>
+          <t>ملاحظات هامة</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="37" t="n"/>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="37" t="n"/>
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="73.5" customHeight="1" s="46">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="50" t="inlineStr">
+        <is>
+          <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
+2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
+3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
+4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="37" t="n"/>
+      <c r="J44" s="38" t="n"/>
+      <c r="K44" s="3" t="n"/>
+    </row>
+    <row r="45" ht="81" customHeight="1" s="46">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="69.75" customHeight="1" s="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="46">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="46"/>
+    <row r="50" ht="31.5" customHeight="1" s="46"/>
+    <row r="51" ht="31.5" customHeight="1" s="46"/>
+    <row r="53" ht="30" customHeight="1" s="46"/>
+    <row r="54" ht="30" customHeight="1" s="46"/>
+    <row r="55" ht="24.75" customHeight="1" s="46"/>
+    <row r="56" ht="24.75" customHeight="1" s="46"/>
+    <row r="57" ht="24.75" customHeight="1" s="46"/>
+    <row r="59" ht="30" customHeight="1" s="46"/>
+    <row r="60" ht="23.25" customHeight="1" s="46"/>
+    <row r="61" ht="24.75" customHeight="1" s="46"/>
+    <row r="62" ht="24.75" customHeight="1" s="46"/>
+    <row r="63" ht="24.75" customHeight="1" s="46"/>
+    <row r="65" ht="30" customHeight="1" s="46"/>
+    <row r="66" ht="20.25" customHeight="1" s="46"/>
+    <row r="67" ht="24.75" customHeight="1" s="46"/>
+    <row r="68" ht="24.75" customHeight="1" s="46"/>
+    <row r="70" ht="30" customHeight="1" s="46"/>
+    <row r="71" ht="30" customHeight="1" s="46"/>
+    <row r="72" ht="24.75" customHeight="1" s="46"/>
+    <row r="73" ht="24.75" customHeight="1" s="46"/>
+    <row r="75" ht="30" customHeight="1" s="46"/>
+    <row r="76" ht="30" customHeight="1" s="46"/>
+    <row r="77" ht="22.5" customHeight="1" s="46"/>
+    <row r="78" ht="23.25" customHeight="1" s="46"/>
+    <row r="79" ht="8.1" customHeight="1" s="46"/>
+    <row r="80" ht="31.5" customHeight="1" s="46"/>
+    <row r="81" ht="15" customHeight="1" s="46"/>
+    <row r="82" ht="15" customHeight="1" s="46"/>
+    <row r="83" ht="75" customHeight="1" s="46"/>
+    <row r="89" ht="14.65" customHeight="1" s="46"/>
+    <row r="90" ht="14.65" customHeight="1" s="46"/>
+    <row r="91" ht="14.65" customHeight="1" s="46"/>
+    <row r="92" ht="14.65" customHeight="1" s="46"/>
+    <row r="93" ht="18.6" customHeight="1" s="46"/>
+    <row r="94" ht="18.6" customHeight="1" s="46"/>
+    <row r="95" ht="18.6" customHeight="1" s="46"/>
+    <row r="96" ht="14.65" customHeight="1" s="46"/>
+    <row r="97" ht="18.6" customHeight="1" s="46"/>
+    <row r="98" ht="18.6" customHeight="1" s="46"/>
+    <row r="99" ht="18.6" customHeight="1" s="46"/>
+    <row r="100" ht="18.6" customHeight="1" s="46"/>
+    <row r="101" ht="18.6" customHeight="1" s="46"/>
+    <row r="102" ht="14.65" customHeight="1" s="46"/>
+    <row r="103" ht="18.6" customHeight="1" s="46"/>
+    <row r="104" ht="18.6" customHeight="1" s="46"/>
+    <row r="105" ht="18.6" customHeight="1" s="46"/>
+    <row r="106" ht="18.6" customHeight="1" s="46"/>
+    <row r="107" ht="18.6" customHeight="1" s="46"/>
+    <row r="108" ht="14.65" customHeight="1" s="46"/>
+    <row r="109" ht="18.6" customHeight="1" s="46"/>
+    <row r="110" ht="14.65" customHeight="1" s="46"/>
+    <row r="111" ht="14.65" customHeight="1" s="46"/>
+    <row r="112" ht="14.65" customHeight="1" s="46"/>
+    <row r="113" ht="18.6" customHeight="1" s="46"/>
+    <row r="114" ht="14.65" customHeight="1" s="46"/>
+    <row r="115" ht="18.6" customHeight="1" s="46"/>
+    <row r="116" ht="18.6" customHeight="1" s="46"/>
+    <row r="117" ht="18.6" customHeight="1" s="46"/>
+    <row r="118" ht="18.6" customHeight="1" s="46"/>
+    <row r="119" ht="18.6" customHeight="1" s="46"/>
+    <row r="120" ht="18.6" customHeight="1" s="46"/>
+    <row r="121" ht="18.6" customHeight="1" s="46"/>
+    <row r="122" ht="18.6" customHeight="1" s="46"/>
+    <row r="123" ht="18.6" customHeight="1" s="46"/>
+    <row r="124" ht="18.6" customHeight="1" s="46"/>
+    <row r="125" ht="18.6" customHeight="1" s="46"/>
+    <row r="126" ht="14.65" customHeight="1" s="46"/>
+    <row r="127" ht="14.65" customHeight="1" s="46"/>
+    <row r="128" ht="14.65" customHeight="1" s="46"/>
+    <row r="129" ht="14.65" customHeight="1" s="46"/>
+    <row r="130" ht="18.6" customHeight="1" s="46"/>
+    <row r="131" ht="18.6" customHeight="1" s="46"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="C43:J43"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E38:H38"/>
+    <mergeCell ref="G9:I9"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="D8:E8"/>
@@ -2642,33 +2661,10 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C43:J43"/>
     <mergeCell ref="I40:J40"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="C6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="1.181102362204725" header="0.31496062992125978" footer="0.31496062992125978"/>
-  <pageSetup paperSize="9" scale="66" fitToHeight="3" orientation="portrait"/>
+  <pageMargins left="0.2362204724409449" right="0.2362204724409449" top="0" bottom="1.181102362204725" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="66" fitToHeight="3"/>
 </worksheet>
 </file>
--- a/po_template.xlsx
+++ b/po_template.xlsx
@@ -347,7 +347,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,12 +502,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1707,7 +1701,7 @@
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="27" t="inlineStr">
         <is>
-          <t>NO. 000001</t>
+          <t>NO. 0144</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1717,7 +1711,7 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
@@ -1771,7 +1765,7 @@
           <t>اسم السائق:</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr"/>
+      <c r="D7" s="36" t="n"/>
       <c r="E7" s="38" t="n"/>
       <c r="F7" s="9" t="inlineStr">
         <is>
@@ -1788,11 +1782,7 @@
           <t>الوظيفة:</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>سائق</t>
-        </is>
-      </c>
+      <c r="I7" s="36" t="n"/>
       <c r="J7" s="38" t="n"/>
       <c r="K7" s="3" t="n"/>
     </row>
@@ -1804,37 +1794,37 @@
           <t>نوع السيارة:</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr"/>
+      <c r="D8" s="58" t="n"/>
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="11" t="inlineStr">
         <is>
           <t>رقم اللوحة:</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="n"/>
       <c r="H8" s="11" t="inlineStr">
         <is>
           <t>الموديل:</t>
         </is>
       </c>
-      <c r="I8" s="40" t="inlineStr"/>
+      <c r="I8" s="40" t="n"/>
       <c r="J8" s="38" t="n"/>
       <c r="K8" s="3" t="n"/>
     </row>
     <row r="9" ht="18.4" customHeight="1" s="46">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n"/>
-      <c r="C9" s="13" t="n"/>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>عداد السيارة:</t>
+        </is>
+      </c>
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="13" t="n"/>
-      <c r="F9" s="62" t="inlineStr">
-        <is>
-          <t>عداد السيارة:</t>
-        </is>
-      </c>
-      <c r="G9" s="63" t="n"/>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="38" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
       <c r="J9" s="13" t="n"/>
       <c r="K9" s="3" t="n"/>
     </row>
@@ -1898,13 +1888,13 @@
       <c r="C12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="36" t="inlineStr"/>
+      <c r="D12" s="36" t="n"/>
       <c r="E12" s="37" t="n"/>
       <c r="F12" s="38" t="n"/>
       <c r="G12" s="36" t="n"/>
       <c r="H12" s="32" t="n"/>
       <c r="I12" s="32" t="n"/>
-      <c r="J12" s="36" t="inlineStr"/>
+      <c r="J12" s="36" t="n"/>
       <c r="K12" s="3" t="n"/>
     </row>
     <row r="13" ht="17.1" customHeight="1" s="46">
@@ -2002,12 +1992,12 @@
       <c r="C18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="36" t="inlineStr"/>
+      <c r="D18" s="36" t="n"/>
       <c r="E18" s="37" t="n"/>
       <c r="F18" s="37" t="n"/>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="inlineStr"/>
+      <c r="I18" s="36" t="n"/>
       <c r="J18" s="38" t="n"/>
       <c r="K18" s="3" t="n"/>
     </row>
@@ -2124,7 +2114,7 @@
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E24" s="36" t="n"/>
@@ -2242,15 +2232,15 @@
       <c r="C30" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="36" t="inlineStr"/>
+      <c r="D30" s="36" t="n"/>
       <c r="E30" s="38" t="n"/>
       <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="inlineStr"/>
-      <c r="H30" s="36" t="inlineStr"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>
@@ -2621,7 +2611,7 @@
     <row r="130" ht="18.6" customHeight="1" s="46"/>
     <row r="131" ht="18.6" customHeight="1" s="46"/>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="39">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="D13:F13"/>
@@ -2648,7 +2638,6 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E38:H38"/>
-    <mergeCell ref="G9:I9"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="D8:E8"/>

--- a/po_template.xlsx
+++ b/po_template.xlsx
@@ -347,7 +347,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,6 +502,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1814,18 +1820,18 @@
     <row r="9" ht="18.4" customHeight="1" s="46">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>عداد السيارة:</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="40" t="n"/>
+      <c r="I9" s="40" t="n"/>
+      <c r="J9" s="63" t="n"/>
       <c r="K9" s="3" t="n"/>
     </row>
     <row r="10" ht="17.45" customHeight="1" s="46">
@@ -2611,7 +2617,7 @@
     <row r="130" ht="18.6" customHeight="1" s="46"/>
     <row r="131" ht="18.6" customHeight="1" s="46"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="D13:F13"/>
@@ -2639,6 +2645,7 @@
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="I8:J8"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="I35:J35"/>

--- a/po_template.xlsx
+++ b/po_template.xlsx
@@ -1,94 +1,252 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC4F59B-53E4-2D4F-80F2-3BED3D6EB3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="نموذج طلب شراء" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="نموذج طلب شراء" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NO. 0144</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
+  </si>
+  <si>
+    <t>بيانات السيارة والسائق</t>
+  </si>
+  <si>
+    <t>اسم السائق:</t>
+  </si>
+  <si>
+    <t>الفرع:</t>
+  </si>
+  <si>
+    <t>الدمام</t>
+  </si>
+  <si>
+    <t>الوظيفة:</t>
+  </si>
+  <si>
+    <t>نوع السيارة:</t>
+  </si>
+  <si>
+    <t>رقم اللوحة:</t>
+  </si>
+  <si>
+    <t>الموديل:</t>
+  </si>
+  <si>
+    <t>قطع الغيار</t>
+  </si>
+  <si>
+    <t>م</t>
+  </si>
+  <si>
+    <t>البيان</t>
+  </si>
+  <si>
+    <t>الكمية</t>
+  </si>
+  <si>
+    <t>السعر</t>
+  </si>
+  <si>
+    <t>القيمة</t>
+  </si>
+  <si>
+    <t>ملاحظات</t>
+  </si>
+  <si>
+    <t>الإصلاح</t>
+  </si>
+  <si>
+    <t>الوصف</t>
+  </si>
+  <si>
+    <t>الكفرات</t>
+  </si>
+  <si>
+    <t>تاريخ التغيير</t>
+  </si>
+  <si>
+    <t>العدد</t>
+  </si>
+  <si>
+    <t>أمامية</t>
+  </si>
+  <si>
+    <t>خلفية</t>
+  </si>
+  <si>
+    <t>قراءة سابقة</t>
+  </si>
+  <si>
+    <t>قراءة حالية</t>
+  </si>
+  <si>
+    <t>المسافة</t>
+  </si>
+  <si>
+    <t>البطاريات</t>
+  </si>
+  <si>
+    <t>المقاس</t>
+  </si>
+  <si>
+    <t>أمبير</t>
+  </si>
+  <si>
+    <t>السعر للوحدة</t>
+  </si>
+  <si>
+    <t>التاريخ</t>
+  </si>
+  <si>
+    <t>الإجمالي شامل الضريبة</t>
+  </si>
+  <si>
+    <t>السائق</t>
+  </si>
+  <si>
+    <t>الميكانيكي</t>
+  </si>
+  <si>
+    <t>قسم الحركة</t>
+  </si>
+  <si>
+    <t>مسئول الشراء</t>
+  </si>
+  <si>
+    <t>الحسابات</t>
+  </si>
+  <si>
+    <t>مدير الفرع</t>
+  </si>
+  <si>
+    <t>اعتماد الإدارة</t>
+  </si>
+  <si>
+    <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
+  </si>
+  <si>
+    <t>ملاحظات هامة</t>
+  </si>
+  <si>
+    <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
+2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
+3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
+4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_ * #,##0.00_)&quot;ر.س.&quot;_ ;_ * \(#,##0.00\)&quot;ر.س.&quot;_ ;_ * &quot;-&quot;??_)&quot;ر.س.&quot;_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;ر.س.&quot;_-;\-* #,##0\ &quot;ر.س.&quot;_-;_-* &quot;-&quot;\ &quot;ر.س.&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Arial"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color indexed="11"/>
       <name val="Helvetica"/>
-      <color indexed="11"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="11"/>
       <name val="Helvetica"/>
-      <b val="1"/>
-      <color indexed="11"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color indexed="8"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="178"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
       <charset val="178"/>
-      <family val="2"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="Sakkal Majalla"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color indexed="8"/>
       <name val="Sakkal Majalla"/>
-      <color indexed="8"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,24 +265,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -310,210 +468,174 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="14"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="64">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="62">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="عادي 2" xfId="2"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -583,6 +705,14 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1660,992 +1790,847 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K47"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="A1:K131"/>
+  <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="8.94921875" customWidth="1" style="46" min="1" max="2"/>
-    <col width="12.01171875" customWidth="1" style="46" min="3" max="3"/>
-    <col width="13.97265625" customWidth="1" style="46" min="4" max="4"/>
-    <col width="12.01171875" customWidth="1" style="46" min="5" max="5"/>
-    <col width="13.97265625" customWidth="1" style="46" min="6" max="7"/>
-    <col width="14.953125" customWidth="1" style="46" min="8" max="8"/>
-    <col width="9.55859375" customWidth="1" style="46" min="9" max="9"/>
-    <col width="19.859375" customWidth="1" style="46" min="10" max="10"/>
-    <col width="8.94921875" customWidth="1" style="46" min="11" max="15"/>
-    <col width="8.82421875" customWidth="1" style="46" min="16" max="17"/>
-    <col width="8.82421875" customWidth="1" style="46" min="18" max="16384"/>
+    <col min="1" max="2" width="8.94921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.01171875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.97265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.01171875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.97265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.55859375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.859375" style="1" customWidth="1"/>
+    <col min="11" max="15" width="8.94921875" style="1" customWidth="1"/>
+    <col min="16" max="17" width="8.82421875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.82421875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" s="46"/>
-    <row r="2" ht="56.25" customHeight="1" s="46">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="13.5" customHeight="1" s="46">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="27" t="inlineStr">
-        <is>
-          <t>NO. 0144</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="27" customHeight="1" s="46" thickBot="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
-        </is>
-      </c>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="52" t="n"/>
-      <c r="H4" s="52" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="9.75" customHeight="1" s="46">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="46">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="42" t="inlineStr">
-        <is>
-          <t>بيانات السيارة والسائق</t>
-        </is>
-      </c>
-      <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-      <c r="G6" s="37" t="n"/>
-      <c r="H6" s="37" t="n"/>
-      <c r="I6" s="37" t="n"/>
-      <c r="J6" s="38" t="n"/>
-      <c r="K6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="21.95" customHeight="1" s="46">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="41" t="inlineStr">
-        <is>
-          <t>اسم السائق:</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="38" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>الفرع:</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>الدمام</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>الوظيفة:</t>
-        </is>
-      </c>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="38" t="n"/>
-      <c r="K7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="18.4" customHeight="1" s="46">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>نوع السيارة:</t>
-        </is>
-      </c>
-      <c r="D8" s="58" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>رقم اللوحة:</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>الموديل:</t>
-        </is>
-      </c>
-      <c r="I8" s="40" t="n"/>
-      <c r="J8" s="38" t="n"/>
-      <c r="K8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="18.4" customHeight="1" s="46">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="62" t="inlineStr">
-        <is>
-          <t>عداد السيارة:</t>
-        </is>
-      </c>
-      <c r="D9" s="58" t="n"/>
-      <c r="E9" s="38" t="n"/>
-      <c r="F9" s="40" t="n"/>
-      <c r="G9" s="40" t="n"/>
-      <c r="H9" s="40" t="n"/>
-      <c r="I9" s="40" t="n"/>
-      <c r="J9" s="63" t="n"/>
-      <c r="K9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="17.45" customHeight="1" s="46">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>قطع الغيار</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="37" t="n"/>
-      <c r="H10" s="37" t="n"/>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="22.35" customHeight="1" s="46">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="41" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>البيان</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>الكمية</t>
-        </is>
-      </c>
-      <c r="H11" s="41" t="inlineStr">
-        <is>
-          <t>السعر</t>
-        </is>
-      </c>
-      <c r="I11" s="41" t="inlineStr">
-        <is>
-          <t>القيمة</t>
-        </is>
-      </c>
-      <c r="J11" s="41" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" s="46">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="24" t="n">
+    <row r="1" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="36" t="n"/>
-      <c r="K12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="17.1" customHeight="1" s="46">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="24" t="n">
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="40" t="n"/>
-      <c r="K13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="17.1" customHeight="1" s="46">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="24" t="n">
+      <c r="D4" s="7"/>
+      <c r="E4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="36" t="n"/>
-      <c r="K14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="17.1" customHeight="1" s="46">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="17.45" customHeight="1" s="46">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>الإصلاح</t>
-        </is>
-      </c>
-      <c r="D16" s="37" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="37" t="n"/>
-      <c r="G16" s="37" t="n"/>
-      <c r="H16" s="37" t="n"/>
-      <c r="I16" s="37" t="n"/>
-      <c r="J16" s="49" t="n"/>
-      <c r="K16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="22.15" customHeight="1" s="46">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="56" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>الوصف</t>
-        </is>
-      </c>
-      <c r="E17" s="59" t="n"/>
-      <c r="F17" s="59" t="n"/>
-      <c r="G17" s="57" t="n"/>
-      <c r="H17" s="56" t="inlineStr">
-        <is>
-          <t>القيمة</t>
-        </is>
-      </c>
-      <c r="I17" s="56" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="J17" s="57" t="n"/>
-      <c r="K17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" s="46">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="24" t="n">
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="36"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="58"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="40"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="24">
         <v>1</v>
       </c>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="17.1" customHeight="1" s="46">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="24" t="n">
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="24">
         <v>2</v>
       </c>
-      <c r="D19" s="40" t="n"/>
-      <c r="E19" s="37" t="n"/>
-      <c r="F19" s="37" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="40" t="n"/>
-      <c r="I19" s="40" t="n"/>
-      <c r="J19" s="38" t="n"/>
-      <c r="K19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="17.1" customHeight="1" s="46">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="24" t="n">
+      <c r="D13" s="40"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="24">
         <v>3</v>
       </c>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="37" t="n"/>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="38" t="n"/>
-      <c r="K20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="17.1" customHeight="1" s="46">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="17.45" customHeight="1" s="46">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>الكفرات</t>
-        </is>
-      </c>
-      <c r="D22" s="37" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="37" t="n"/>
-      <c r="G22" s="37" t="n"/>
-      <c r="H22" s="37" t="n"/>
-      <c r="I22" s="37" t="n"/>
-      <c r="J22" s="38" t="n"/>
-      <c r="K22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="22.15" customHeight="1" s="46">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>تاريخ التغيير</t>
-        </is>
-      </c>
-      <c r="E23" s="41" t="inlineStr">
-        <is>
-          <t>العدد</t>
-        </is>
-      </c>
-      <c r="F23" s="41" t="inlineStr">
-        <is>
-          <t>أمامية</t>
-        </is>
-      </c>
-      <c r="G23" s="41" t="inlineStr">
-        <is>
-          <t>خلفية</t>
-        </is>
-      </c>
-      <c r="H23" s="41" t="inlineStr">
-        <is>
-          <t>قراءة سابقة</t>
-        </is>
-      </c>
-      <c r="I23" s="41" t="inlineStr">
-        <is>
-          <t>قراءة حالية</t>
-        </is>
-      </c>
-      <c r="J23" s="41" t="inlineStr">
-        <is>
-          <t>المسافة</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="18.95" customHeight="1" s="46">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="24" t="n">
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="57"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="24">
         <v>1</v>
       </c>
-      <c r="D24" s="36" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="17.1" customHeight="1" s="46">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="24" t="n">
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="24">
         <v>2</v>
       </c>
-      <c r="D25" s="40" t="n"/>
-      <c r="E25" s="40" t="n"/>
-      <c r="F25" s="40" t="n"/>
-      <c r="G25" s="40" t="n"/>
-      <c r="H25" s="40" t="n"/>
-      <c r="I25" s="40" t="n"/>
-      <c r="J25" s="40" t="n"/>
-      <c r="K25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="17.1" customHeight="1" s="46">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="24" t="n">
+      <c r="D19" s="40"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="24">
         <v>3</v>
       </c>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="3" t="n"/>
-    </row>
-    <row r="27" ht="17.1" customHeight="1" s="46">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="3" t="n"/>
-    </row>
-    <row r="28" ht="17.45" customHeight="1" s="46">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="47" t="inlineStr">
-        <is>
-          <t>البطاريات</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
-      <c r="H28" s="37" t="n"/>
-      <c r="I28" s="37" t="n"/>
-      <c r="J28" s="38" t="n"/>
-      <c r="K28" s="3" t="n"/>
-    </row>
-    <row r="29" ht="22.15" customHeight="1" s="46">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="41" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="D29" s="41" t="inlineStr">
-        <is>
-          <t>الوصف</t>
-        </is>
-      </c>
-      <c r="E29" s="38" t="n"/>
-      <c r="F29" s="41" t="inlineStr">
-        <is>
-          <t>العدد</t>
-        </is>
-      </c>
-      <c r="G29" s="41" t="inlineStr">
-        <is>
-          <t>المقاس</t>
-        </is>
-      </c>
-      <c r="H29" s="41" t="inlineStr">
-        <is>
-          <t>أمبير</t>
-        </is>
-      </c>
-      <c r="I29" s="41" t="inlineStr">
-        <is>
-          <t>السعر للوحدة</t>
-        </is>
-      </c>
-      <c r="J29" s="41" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
-    </row>
-    <row r="30" ht="18.95" customHeight="1" s="46">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="24" t="n">
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="24">
         <v>1</v>
       </c>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="38" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="n"/>
-    </row>
-    <row r="31" ht="17.1" customHeight="1" s="46">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="24" t="n">
+      <c r="D24" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="38" t="n"/>
-      <c r="F31" s="40" t="n"/>
-      <c r="G31" s="40" t="n"/>
-      <c r="H31" s="40" t="n"/>
-      <c r="I31" s="40" t="n"/>
-      <c r="J31" s="40" t="n"/>
-      <c r="K31" s="3" t="n"/>
-    </row>
-    <row r="32" ht="17.1" customHeight="1" s="46">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="24" t="n">
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="24">
+        <v>2</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="24">
         <v>3</v>
       </c>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="38" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="3" t="n"/>
-    </row>
-    <row r="33" ht="17.1" customHeight="1" s="46">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="45" t="n"/>
-      <c r="D33" s="45" t="n"/>
-      <c r="F33" s="45" t="n"/>
-      <c r="G33" s="45" t="n"/>
-      <c r="H33" s="45" t="n"/>
-      <c r="I33" s="45" t="n"/>
-      <c r="J33" s="45" t="n"/>
-      <c r="K33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="18.95" customHeight="1" s="46">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="39" t="inlineStr">
-        <is>
-          <t>قطع الغيار</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>الإصلاح</t>
-        </is>
-      </c>
-      <c r="E34" s="39" t="inlineStr">
-        <is>
-          <t>الكفرات</t>
-        </is>
-      </c>
-      <c r="F34" s="39" t="inlineStr">
-        <is>
-          <t>البطاريات</t>
-        </is>
-      </c>
-      <c r="G34" s="39" t="inlineStr">
-        <is>
-          <t>الإجمالي شامل الضريبة</t>
-        </is>
-      </c>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="39" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-      <c r="J34" s="38" t="n"/>
-      <c r="K34" s="3" t="n"/>
-    </row>
-    <row r="35" ht="17.65" customHeight="1" s="46">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="38" t="n"/>
-      <c r="K35" s="3" t="n"/>
-    </row>
-    <row r="36" ht="17.1" customHeight="1" s="46">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="45" t="n"/>
-      <c r="E36" s="45" t="n"/>
-      <c r="F36" s="45" t="n"/>
-      <c r="G36" s="45" t="n"/>
-      <c r="I36" s="45" t="n"/>
-      <c r="K36" s="3" t="n"/>
-    </row>
-    <row r="37" ht="18.6" customHeight="1" s="46">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="39" t="inlineStr">
-        <is>
-          <t>الإجمالي شامل الضريبة</t>
-        </is>
-      </c>
-      <c r="D37" s="38" t="n"/>
-      <c r="E37" s="53" t="n"/>
-      <c r="F37" s="37" t="n"/>
-      <c r="G37" s="37" t="n"/>
-      <c r="H37" s="37" t="n"/>
-      <c r="I37" s="37" t="n"/>
-      <c r="J37" s="38" t="n"/>
-      <c r="K37" s="3" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="46" thickBot="1">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="54" t="n"/>
-      <c r="F38" s="55" t="n"/>
-      <c r="G38" s="55" t="n"/>
-      <c r="H38" s="55" t="n"/>
-      <c r="I38" s="18" t="n"/>
-      <c r="J38" s="18" t="n"/>
-      <c r="K38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="5.25" customHeight="1" s="46">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40" ht="21" customFormat="1" customHeight="1" s="31">
-      <c r="A40" s="29" t="n"/>
-      <c r="B40" s="30" t="n"/>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>السائق</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="inlineStr">
-        <is>
-          <t>الميكانيكي</t>
-        </is>
-      </c>
-      <c r="E40" s="28" t="inlineStr">
-        <is>
-          <t>قسم الحركة</t>
-        </is>
-      </c>
-      <c r="F40" s="28" t="inlineStr">
-        <is>
-          <t>مسئول الشراء</t>
-        </is>
-      </c>
-      <c r="G40" s="28" t="inlineStr">
-        <is>
-          <t>الحسابات</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>مدير الفرع</t>
-        </is>
-      </c>
-      <c r="I40" s="60" t="inlineStr">
-        <is>
-          <t>اعتماد الإدارة</t>
-        </is>
-      </c>
-      <c r="J40" s="61" t="n"/>
-      <c r="K40" s="30" t="n"/>
-    </row>
-    <row r="41" ht="63" customHeight="1" s="46" thickBot="1">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="18" t="n"/>
-      <c r="K41" s="3" t="n"/>
-    </row>
-    <row r="42" ht="17.25" customHeight="1" s="46">
-      <c r="A42" s="2" t="n"/>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
-        </is>
-      </c>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="44" t="n"/>
-      <c r="F42" s="44" t="n"/>
-      <c r="G42" s="44" t="n"/>
-      <c r="H42" s="44" t="n"/>
-      <c r="I42" s="44" t="n"/>
-      <c r="J42" s="44" t="n"/>
-      <c r="K42" s="3" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="46">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="47" t="inlineStr">
-        <is>
-          <t>ملاحظات هامة</t>
-        </is>
-      </c>
-      <c r="D43" s="37" t="n"/>
-      <c r="E43" s="37" t="n"/>
-      <c r="F43" s="37" t="n"/>
-      <c r="G43" s="37" t="n"/>
-      <c r="H43" s="37" t="n"/>
-      <c r="I43" s="37" t="n"/>
-      <c r="J43" s="38" t="n"/>
-      <c r="K43" s="3" t="n"/>
-    </row>
-    <row r="44" ht="73.5" customHeight="1" s="46">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="50" t="inlineStr">
-        <is>
-          <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
-2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
-3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
-4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
-        </is>
-      </c>
-      <c r="D44" s="37" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="37" t="n"/>
-      <c r="G44" s="37" t="n"/>
-      <c r="H44" s="37" t="n"/>
-      <c r="I44" s="37" t="n"/>
-      <c r="J44" s="38" t="n"/>
-      <c r="K44" s="3" t="n"/>
-    </row>
-    <row r="45" ht="81" customHeight="1" s="46">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-    </row>
-    <row r="46" ht="69.75" customHeight="1" s="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1" s="46">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-    </row>
-    <row r="49" ht="30" customHeight="1" s="46"/>
-    <row r="50" ht="31.5" customHeight="1" s="46"/>
-    <row r="51" ht="31.5" customHeight="1" s="46"/>
-    <row r="53" ht="30" customHeight="1" s="46"/>
-    <row r="54" ht="30" customHeight="1" s="46"/>
-    <row r="55" ht="24.75" customHeight="1" s="46"/>
-    <row r="56" ht="24.75" customHeight="1" s="46"/>
-    <row r="57" ht="24.75" customHeight="1" s="46"/>
-    <row r="59" ht="30" customHeight="1" s="46"/>
-    <row r="60" ht="23.25" customHeight="1" s="46"/>
-    <row r="61" ht="24.75" customHeight="1" s="46"/>
-    <row r="62" ht="24.75" customHeight="1" s="46"/>
-    <row r="63" ht="24.75" customHeight="1" s="46"/>
-    <row r="65" ht="30" customHeight="1" s="46"/>
-    <row r="66" ht="20.25" customHeight="1" s="46"/>
-    <row r="67" ht="24.75" customHeight="1" s="46"/>
-    <row r="68" ht="24.75" customHeight="1" s="46"/>
-    <row r="70" ht="30" customHeight="1" s="46"/>
-    <row r="71" ht="30" customHeight="1" s="46"/>
-    <row r="72" ht="24.75" customHeight="1" s="46"/>
-    <row r="73" ht="24.75" customHeight="1" s="46"/>
-    <row r="75" ht="30" customHeight="1" s="46"/>
-    <row r="76" ht="30" customHeight="1" s="46"/>
-    <row r="77" ht="22.5" customHeight="1" s="46"/>
-    <row r="78" ht="23.25" customHeight="1" s="46"/>
-    <row r="79" ht="8.1" customHeight="1" s="46"/>
-    <row r="80" ht="31.5" customHeight="1" s="46"/>
-    <row r="81" ht="15" customHeight="1" s="46"/>
-    <row r="82" ht="15" customHeight="1" s="46"/>
-    <row r="83" ht="75" customHeight="1" s="46"/>
-    <row r="89" ht="14.65" customHeight="1" s="46"/>
-    <row r="90" ht="14.65" customHeight="1" s="46"/>
-    <row r="91" ht="14.65" customHeight="1" s="46"/>
-    <row r="92" ht="14.65" customHeight="1" s="46"/>
-    <row r="93" ht="18.6" customHeight="1" s="46"/>
-    <row r="94" ht="18.6" customHeight="1" s="46"/>
-    <row r="95" ht="18.6" customHeight="1" s="46"/>
-    <row r="96" ht="14.65" customHeight="1" s="46"/>
-    <row r="97" ht="18.6" customHeight="1" s="46"/>
-    <row r="98" ht="18.6" customHeight="1" s="46"/>
-    <row r="99" ht="18.6" customHeight="1" s="46"/>
-    <row r="100" ht="18.6" customHeight="1" s="46"/>
-    <row r="101" ht="18.6" customHeight="1" s="46"/>
-    <row r="102" ht="14.65" customHeight="1" s="46"/>
-    <row r="103" ht="18.6" customHeight="1" s="46"/>
-    <row r="104" ht="18.6" customHeight="1" s="46"/>
-    <row r="105" ht="18.6" customHeight="1" s="46"/>
-    <row r="106" ht="18.6" customHeight="1" s="46"/>
-    <row r="107" ht="18.6" customHeight="1" s="46"/>
-    <row r="108" ht="14.65" customHeight="1" s="46"/>
-    <row r="109" ht="18.6" customHeight="1" s="46"/>
-    <row r="110" ht="14.65" customHeight="1" s="46"/>
-    <row r="111" ht="14.65" customHeight="1" s="46"/>
-    <row r="112" ht="14.65" customHeight="1" s="46"/>
-    <row r="113" ht="18.6" customHeight="1" s="46"/>
-    <row r="114" ht="14.65" customHeight="1" s="46"/>
-    <row r="115" ht="18.6" customHeight="1" s="46"/>
-    <row r="116" ht="18.6" customHeight="1" s="46"/>
-    <row r="117" ht="18.6" customHeight="1" s="46"/>
-    <row r="118" ht="18.6" customHeight="1" s="46"/>
-    <row r="119" ht="18.6" customHeight="1" s="46"/>
-    <row r="120" ht="18.6" customHeight="1" s="46"/>
-    <row r="121" ht="18.6" customHeight="1" s="46"/>
-    <row r="122" ht="18.6" customHeight="1" s="46"/>
-    <row r="123" ht="18.6" customHeight="1" s="46"/>
-    <row r="124" ht="18.6" customHeight="1" s="46"/>
-    <row r="125" ht="18.6" customHeight="1" s="46"/>
-    <row r="126" ht="14.65" customHeight="1" s="46"/>
-    <row r="127" ht="14.65" customHeight="1" s="46"/>
-    <row r="128" ht="14.65" customHeight="1" s="46"/>
-    <row r="129" ht="14.65" customHeight="1" s="46"/>
-    <row r="130" ht="18.6" customHeight="1" s="46"/>
-    <row r="131" ht="18.6" customHeight="1" s="46"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="24">
+        <v>1</v>
+      </c>
+      <c r="D30" s="36"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="24">
+        <v>2</v>
+      </c>
+      <c r="D31" s="40"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="24">
+        <v>3</v>
+      </c>
+      <c r="D32" s="36"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="38"/>
+      <c r="I34" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="38"/>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="38"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="8"/>
+    </row>
+    <row r="40" spans="1:11" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="61"/>
+      <c r="K40" s="30"/>
+    </row>
+    <row r="41" spans="1:11" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="2"/>
+      <c r="C42" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="3"/>
+    </row>
+    <row r="45" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+    </row>
+    <row r="46" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C43:J43"/>
+  <mergeCells count="39">
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="D9:E9"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="I35:J35"/>
@@ -2657,10 +2642,33 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C43:J43"/>
     <mergeCell ref="I40:J40"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="C6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.2362204724409449" right="0.2362204724409449" top="0" bottom="1.181102362204725" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="66" fitToHeight="3"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="1.181102362204725" header="0.31496062992125978" footer="0.31496062992125978"/>
+  <pageSetup paperSize="9" scale="66" fitToHeight="3" orientation="portrait"/>
 </worksheet>
 </file>
--- a/po_template.xlsx
+++ b/po_template.xlsx
@@ -1,252 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC4F59B-53E4-2D4F-80F2-3BED3D6EB3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="نموذج طلب شراء" sheetId="1" r:id="rId1"/>
+    <sheet name="نموذج طلب شراء" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>NO. 0144</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
-  </si>
-  <si>
-    <t>بيانات السيارة والسائق</t>
-  </si>
-  <si>
-    <t>اسم السائق:</t>
-  </si>
-  <si>
-    <t>الفرع:</t>
-  </si>
-  <si>
-    <t>الدمام</t>
-  </si>
-  <si>
-    <t>الوظيفة:</t>
-  </si>
-  <si>
-    <t>نوع السيارة:</t>
-  </si>
-  <si>
-    <t>رقم اللوحة:</t>
-  </si>
-  <si>
-    <t>الموديل:</t>
-  </si>
-  <si>
-    <t>قطع الغيار</t>
-  </si>
-  <si>
-    <t>م</t>
-  </si>
-  <si>
-    <t>البيان</t>
-  </si>
-  <si>
-    <t>الكمية</t>
-  </si>
-  <si>
-    <t>السعر</t>
-  </si>
-  <si>
-    <t>القيمة</t>
-  </si>
-  <si>
-    <t>ملاحظات</t>
-  </si>
-  <si>
-    <t>الإصلاح</t>
-  </si>
-  <si>
-    <t>الوصف</t>
-  </si>
-  <si>
-    <t>الكفرات</t>
-  </si>
-  <si>
-    <t>تاريخ التغيير</t>
-  </si>
-  <si>
-    <t>العدد</t>
-  </si>
-  <si>
-    <t>أمامية</t>
-  </si>
-  <si>
-    <t>خلفية</t>
-  </si>
-  <si>
-    <t>قراءة سابقة</t>
-  </si>
-  <si>
-    <t>قراءة حالية</t>
-  </si>
-  <si>
-    <t>المسافة</t>
-  </si>
-  <si>
-    <t>البطاريات</t>
-  </si>
-  <si>
-    <t>المقاس</t>
-  </si>
-  <si>
-    <t>أمبير</t>
-  </si>
-  <si>
-    <t>السعر للوحدة</t>
-  </si>
-  <si>
-    <t>التاريخ</t>
-  </si>
-  <si>
-    <t>الإجمالي شامل الضريبة</t>
-  </si>
-  <si>
-    <t>السائق</t>
-  </si>
-  <si>
-    <t>الميكانيكي</t>
-  </si>
-  <si>
-    <t>قسم الحركة</t>
-  </si>
-  <si>
-    <t>مسئول الشراء</t>
-  </si>
-  <si>
-    <t>الحسابات</t>
-  </si>
-  <si>
-    <t>مدير الفرع</t>
-  </si>
-  <si>
-    <t>اعتماد الإدارة</t>
-  </si>
-  <si>
-    <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
-  </si>
-  <si>
-    <t>ملاحظات هامة</t>
-  </si>
-  <si>
-    <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
-2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
-3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
-4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_ * #,##0.00_)&quot;ر.س.&quot;_ ;_ * \(#,##0.00\)&quot;ر.س.&quot;_ ;_ * &quot;-&quot;??_)&quot;ر.س.&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;ر.س.&quot;_-;\-* #,##0\ &quot;ر.س.&quot;_-;_-* &quot;-&quot;\ &quot;ر.س.&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
+      <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Helvetica"/>
+      <color indexed="11"/>
       <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Helvetica"/>
     </font>
     <font>
-      <b/>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color indexed="11"/>
       <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Helvetica"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="178"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="178"/>
+      <family val="2"/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="178"/>
     </font>
     <font>
-      <b/>
+      <name val="Sakkal Majalla"/>
+      <b val="1"/>
       <sz val="12"/>
-      <name val="Sakkal Majalla"/>
     </font>
     <font>
+      <name val="Sakkal Majalla"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Sakkal Majalla"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -265,24 +107,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -468,174 +310,210 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="62">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="64">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
-    <cellStyle name="عادي 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="عادي 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -705,14 +583,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1790,847 +1660,992 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
-  <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A2:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="8.94921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.01171875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.97265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.01171875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.97265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.55859375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.859375" style="1" customWidth="1"/>
-    <col min="11" max="15" width="8.94921875" style="1" customWidth="1"/>
-    <col min="16" max="17" width="8.82421875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.82421875" style="1"/>
+    <col width="8.94921875" customWidth="1" style="46" min="1" max="2"/>
+    <col width="12.01171875" customWidth="1" style="46" min="3" max="3"/>
+    <col width="13.97265625" customWidth="1" style="46" min="4" max="4"/>
+    <col width="12.01171875" customWidth="1" style="46" min="5" max="5"/>
+    <col width="13.97265625" customWidth="1" style="46" min="6" max="7"/>
+    <col width="14.953125" customWidth="1" style="46" min="8" max="8"/>
+    <col width="9.55859375" customWidth="1" style="46" min="9" max="9"/>
+    <col width="19.859375" customWidth="1" style="46" min="10" max="10"/>
+    <col width="8.94921875" customWidth="1" style="46" min="11" max="15"/>
+    <col width="8.82421875" customWidth="1" style="46" min="16" max="17"/>
+    <col width="8.82421875" customWidth="1" style="46" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="27" t="s">
+    <row r="1" ht="35.25" customHeight="1" s="46"/>
+    <row r="2" ht="56.25" customHeight="1" s="46">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" s="46">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="27" t="inlineStr">
+        <is>
+          <t>NO. 0144</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="27" customHeight="1" s="46" thickBot="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        نموذج طلب شراء وإصلاح سيارة  </t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="n"/>
+      <c r="G4" s="52" t="n"/>
+      <c r="H4" s="52" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="9.75" customHeight="1" s="46">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="46">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>بيانات السيارة والسائق</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="38" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="21.95" customHeight="1" s="46">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>اسم السائق:</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>الفرع:</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>الدمام</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>الوظيفة:</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="18.4" customHeight="1" s="46">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>نوع السيارة:</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>رقم اللوحة:</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>الموديل:</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="n"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18.4" customHeight="1" s="46">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>عداد السيارة:</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="40" t="n"/>
+      <c r="I9" s="40" t="n"/>
+      <c r="J9" s="63" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="17.45" customHeight="1" s="46">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>قطع الغيار</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="22.35" customHeight="1" s="46">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>البيان</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>السعر</t>
+        </is>
+      </c>
+      <c r="I11" s="41" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="J11" s="41" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="18.95" customHeight="1" s="46">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="17.1" customHeight="1" s="46">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="51" t="s">
+      <c r="D13" s="40" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="33" t="n"/>
+      <c r="I13" s="33" t="n"/>
+      <c r="J13" s="40" t="n"/>
+      <c r="K13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="17.1" customHeight="1" s="46">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="24">
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="17.1" customHeight="1" s="46">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="17.45" customHeight="1" s="46">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>الإصلاح</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="22.15" customHeight="1" s="46">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="56" t="inlineStr">
+        <is>
+          <t>القيمة</t>
+        </is>
+      </c>
+      <c r="I17" s="56" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="J17" s="57" t="n"/>
+      <c r="K17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="18.95" customHeight="1" s="46">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="24">
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="17.1" customHeight="1" s="46">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="24">
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="40" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="17.1" customHeight="1" s="46">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="57"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="24">
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="38" t="n"/>
+      <c r="K20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="17.1" customHeight="1" s="46">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="17.45" customHeight="1" s="46">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>الكفرات</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="38" t="n"/>
+      <c r="K22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="22.15" customHeight="1" s="46">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>تاريخ التغيير</t>
+        </is>
+      </c>
+      <c r="E23" s="41" t="inlineStr">
+        <is>
+          <t>العدد</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="inlineStr">
+        <is>
+          <t>أمامية</t>
+        </is>
+      </c>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>خلفية</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="inlineStr">
+        <is>
+          <t>قراءة سابقة</t>
+        </is>
+      </c>
+      <c r="I23" s="41" t="inlineStr">
+        <is>
+          <t>قراءة حالية</t>
+        </is>
+      </c>
+      <c r="J23" s="41" t="inlineStr">
+        <is>
+          <t>المسافة</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="18.95" customHeight="1" s="46">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="24">
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="17.1" customHeight="1" s="46">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="24">
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="17.1" customHeight="1" s="46">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="24">
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="17.1" customHeight="1" s="46">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="17.45" customHeight="1" s="46">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>البطاريات</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="37" t="n"/>
+      <c r="H28" s="37" t="n"/>
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="38" t="n"/>
+      <c r="K28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="22.15" customHeight="1" s="46">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>العدد</t>
+        </is>
+      </c>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>المقاس</t>
+        </is>
+      </c>
+      <c r="H29" s="41" t="inlineStr">
+        <is>
+          <t>أمبير</t>
+        </is>
+      </c>
+      <c r="I29" s="41" t="inlineStr">
+        <is>
+          <t>السعر للوحدة</t>
+        </is>
+      </c>
+      <c r="J29" s="41" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="18.95" customHeight="1" s="46">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="38" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="17.1" customHeight="1" s="46">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="24">
-        <v>2</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="24">
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="40" t="n"/>
+      <c r="I31" s="40" t="n"/>
+      <c r="J31" s="40" t="n"/>
+      <c r="K31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="17.1" customHeight="1" s="46">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="24">
-        <v>1</v>
-      </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="24">
-        <v>2</v>
-      </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="24">
-        <v>3</v>
-      </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="1:11" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="3"/>
-    </row>
-    <row r="37" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="38" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="3"/>
-    </row>
-    <row r="39" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="8"/>
-    </row>
-    <row r="40" spans="1:11" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="29"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F40" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I40" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="61"/>
-      <c r="K40" s="30"/>
-    </row>
-    <row r="41" spans="1:11" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="2"/>
-      <c r="C42" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="14.65" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="17.1" customHeight="1" s="46">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="45" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="45" t="n"/>
+      <c r="H33" s="45" t="n"/>
+      <c r="I33" s="45" t="n"/>
+      <c r="J33" s="45" t="n"/>
+      <c r="K33" s="3" t="n"/>
+    </row>
+    <row r="34" ht="18.95" customHeight="1" s="46">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>قطع الغيار</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>الإصلاح</t>
+        </is>
+      </c>
+      <c r="E34" s="39" t="inlineStr">
+        <is>
+          <t>الكفرات</t>
+        </is>
+      </c>
+      <c r="F34" s="39" t="inlineStr">
+        <is>
+          <t>البطاريات</t>
+        </is>
+      </c>
+      <c r="G34" s="39" t="inlineStr">
+        <is>
+          <t>الإجمالي شامل الضريبة</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="39" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="n"/>
+      <c r="K34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="17.65" customHeight="1" s="46">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="35" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="38" t="n"/>
+      <c r="K35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="17.1" customHeight="1" s="46">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="I36" s="45" t="n"/>
+      <c r="K36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="18.6" customHeight="1" s="46">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>الإجمالي شامل الضريبة</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="37" t="n"/>
+      <c r="G37" s="37" t="n"/>
+      <c r="H37" s="37" t="n"/>
+      <c r="I37" s="37" t="n"/>
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="46" thickBot="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="55" t="n"/>
+      <c r="H38" s="55" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="5.25" customHeight="1" s="46">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="21" customFormat="1" customHeight="1" s="31">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>السائق</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>الميكانيكي</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>قسم الحركة</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
+          <t>مسئول الشراء</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>الحسابات</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>مدير الفرع</t>
+        </is>
+      </c>
+      <c r="I40" s="60" t="inlineStr">
+        <is>
+          <t>اعتماد الإدارة</t>
+        </is>
+      </c>
+      <c r="J40" s="61" t="n"/>
+      <c r="K40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="63" customHeight="1" s="46" thickBot="1">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="17.25" customHeight="1" s="46">
+      <c r="A42" s="2" t="n"/>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>تم إعداد هذا الجدول بواسطة قسم الحركة</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="44" t="n"/>
+      <c r="H42" s="44" t="n"/>
+      <c r="I42" s="44" t="n"/>
+      <c r="J42" s="44" t="n"/>
+      <c r="K42" s="3" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="46">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="47" t="inlineStr">
+        <is>
+          <t>ملاحظات هامة</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="37" t="n"/>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="37" t="n"/>
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="73.5" customHeight="1" s="46">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="50" t="inlineStr">
+        <is>
+          <t>1ـ يعبأ الطلب من قبل مسئول الورشة بعد توقيعه وتوقيع السائق والميكانيكي 
+2ـ يوقع بعد ذلك من المحاسبة ويتم ارساله للإدارة عن طريق محاسب الفرع ليتم اعتماده من الإدارة 
+3ـ عند وجود ملاحظة لأي من الأطراف يمكن تدوينها في حقل الملاحظات أعلاه
+4ـ ترفق صورة للإدارة المالية وصورة لقسم الحركة بالإدارة، ويتم حفظ صورة من الطلب لدى الورشة</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="37" t="n"/>
+      <c r="J44" s="38" t="n"/>
+      <c r="K44" s="3" t="n"/>
+    </row>
+    <row r="45" ht="81" customHeight="1" s="46">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="69.75" customHeight="1" s="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="46">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="46"/>
+    <row r="50" ht="31.5" customHeight="1" s="46"/>
+    <row r="51" ht="31.5" customHeight="1" s="46"/>
+    <row r="53" ht="30" customHeight="1" s="46"/>
+    <row r="54" ht="30" customHeight="1" s="46"/>
+    <row r="55" ht="24.75" customHeight="1" s="46"/>
+    <row r="56" ht="24.75" customHeight="1" s="46"/>
+    <row r="57" ht="24.75" customHeight="1" s="46"/>
+    <row r="59" ht="30" customHeight="1" s="46"/>
+    <row r="60" ht="23.25" customHeight="1" s="46"/>
+    <row r="61" ht="24.75" customHeight="1" s="46"/>
+    <row r="62" ht="24.75" customHeight="1" s="46"/>
+    <row r="63" ht="24.75" customHeight="1" s="46"/>
+    <row r="65" ht="30" customHeight="1" s="46"/>
+    <row r="66" ht="20.25" customHeight="1" s="46"/>
+    <row r="67" ht="24.75" customHeight="1" s="46"/>
+    <row r="68" ht="24.75" customHeight="1" s="46"/>
+    <row r="70" ht="30" customHeight="1" s="46"/>
+    <row r="71" ht="30" customHeight="1" s="46"/>
+    <row r="72" ht="24.75" customHeight="1" s="46"/>
+    <row r="73" ht="24.75" customHeight="1" s="46"/>
+    <row r="75" ht="30" customHeight="1" s="46"/>
+    <row r="76" ht="30" customHeight="1" s="46"/>
+    <row r="77" ht="22.5" customHeight="1" s="46"/>
+    <row r="78" ht="23.25" customHeight="1" s="46"/>
+    <row r="79" ht="8.1" customHeight="1" s="46"/>
+    <row r="80" ht="31.5" customHeight="1" s="46"/>
+    <row r="81" ht="15" customHeight="1" s="46"/>
+    <row r="82" ht="15" customHeight="1" s="46"/>
+    <row r="83" ht="75" customHeight="1" s="46"/>
+    <row r="89" ht="14.65" customHeight="1" s="46"/>
+    <row r="90" ht="14.65" customHeight="1" s="46"/>
+    <row r="91" ht="14.65" customHeight="1" s="46"/>
+    <row r="92" ht="14.65" customHeight="1" s="46"/>
+    <row r="93" ht="18.6" customHeight="1" s="46"/>
+    <row r="94" ht="18.6" customHeight="1" s="46"/>
+    <row r="95" ht="18.6" customHeight="1" s="46"/>
+    <row r="96" ht="14.65" customHeight="1" s="46"/>
+    <row r="97" ht="18.6" customHeight="1" s="46"/>
+    <row r="98" ht="18.6" customHeight="1" s="46"/>
+    <row r="99" ht="18.6" customHeight="1" s="46"/>
+    <row r="100" ht="18.6" customHeight="1" s="46"/>
+    <row r="101" ht="18.6" customHeight="1" s="46"/>
+    <row r="102" ht="14.65" customHeight="1" s="46"/>
+    <row r="103" ht="18.6" customHeight="1" s="46"/>
+    <row r="104" ht="18.6" customHeight="1" s="46"/>
+    <row r="105" ht="18.6" customHeight="1" s="46"/>
+    <row r="106" ht="18.6" customHeight="1" s="46"/>
+    <row r="107" ht="18.6" customHeight="1" s="46"/>
+    <row r="108" ht="14.65" customHeight="1" s="46"/>
+    <row r="109" ht="18.6" customHeight="1" s="46"/>
+    <row r="110" ht="14.65" customHeight="1" s="46"/>
+    <row r="111" ht="14.65" customHeight="1" s="46"/>
+    <row r="112" ht="14.65" customHeight="1" s="46"/>
+    <row r="113" ht="18.6" customHeight="1" s="46"/>
+    <row r="114" ht="14.65" customHeight="1" s="46"/>
+    <row r="115" ht="18.6" customHeight="1" s="46"/>
+    <row r="116" ht="18.6" customHeight="1" s="46"/>
+    <row r="117" ht="18.6" customHeight="1" s="46"/>
+    <row r="118" ht="18.6" customHeight="1" s="46"/>
+    <row r="119" ht="18.6" customHeight="1" s="46"/>
+    <row r="120" ht="18.6" customHeight="1" s="46"/>
+    <row r="121" ht="18.6" customHeight="1" s="46"/>
+    <row r="122" ht="18.6" customHeight="1" s="46"/>
+    <row r="123" ht="18.6" customHeight="1" s="46"/>
+    <row r="124" ht="18.6" customHeight="1" s="46"/>
+    <row r="125" ht="18.6" customHeight="1" s="46"/>
+    <row r="126" ht="14.65" customHeight="1" s="46"/>
+    <row r="127" ht="14.65" customHeight="1" s="46"/>
+    <row r="128" ht="14.65" customHeight="1" s="46"/>
+    <row r="129" ht="14.65" customHeight="1" s="46"/>
+    <row r="130" ht="18.6" customHeight="1" s="46"/>
+    <row r="131" ht="18.6" customHeight="1" s="46"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="C43:J43"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="I8:J8"/>
+    <mergeCell ref="D9:E9"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="I35:J35"/>
@@ -2642,33 +2657,10 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="C43:J43"/>
     <mergeCell ref="I40:J40"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="C6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="1.181102362204725" header="0.31496062992125978" footer="0.31496062992125978"/>
-  <pageSetup paperSize="9" scale="66" fitToHeight="3" orientation="portrait"/>
+  <pageMargins left="0.2362204724409449" right="0.2362204724409449" top="0" bottom="1.181102362204725" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="66" fitToHeight="3"/>
 </worksheet>
 </file>